--- a/verification/registry-records.xlsx
+++ b/verification/registry-records.xlsx
@@ -2578,18 +2578,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblRegistry" displayName="tblRegistry" ref="A1:S518" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="A1:S518" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="OPVAL"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="12">
-      <filters>
-        <filter val="No"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S518" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Record ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cell ID"/>
@@ -3375,7 +3364,7 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1">
+    <row r="2" spans="1:19">
       <c r="A2" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E001</t>
@@ -3444,7 +3433,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1">
+    <row r="3" spans="1:19">
       <c r="A3" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E002</t>
@@ -3514,7 +3503,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1">
+    <row r="4" spans="1:19">
       <c r="A4" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E003</t>
@@ -3584,7 +3573,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1">
+    <row r="5" spans="1:19">
       <c r="A5" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E004</t>
@@ -3654,7 +3643,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1">
+    <row r="6" spans="1:19">
       <c r="A6" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E005</t>
@@ -3724,7 +3713,7 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1">
+    <row r="7" spans="1:19">
       <c r="A7" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E006</t>
@@ -3794,7 +3783,7 @@
         </is>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1">
+    <row r="8" spans="1:19">
       <c r="A8" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E007</t>
@@ -3863,7 +3852,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1">
+    <row r="9" spans="1:19">
       <c r="A9" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E008</t>
@@ -3933,7 +3922,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1">
+    <row r="10" spans="1:19">
       <c r="A10" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E009</t>
@@ -4003,7 +3992,7 @@
         </is>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1">
+    <row r="11" spans="1:19">
       <c r="A11" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E010</t>
@@ -4073,7 +4062,7 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1">
+    <row r="12" spans="1:19">
       <c r="A12" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E011</t>
@@ -4146,7 +4135,7 @@
         </is>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1">
+    <row r="13" spans="1:19">
       <c r="A13" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-NT-E012</t>
@@ -4219,7 +4208,7 @@
         </is>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1">
+    <row r="14" spans="1:19">
       <c r="A14" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E001</t>
@@ -4289,7 +4278,7 @@
         </is>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1">
+    <row r="15" spans="1:19">
       <c r="A15" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E002</t>
@@ -4359,7 +4348,7 @@
         </is>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1">
+    <row r="16" spans="1:19">
       <c r="A16" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E003</t>
@@ -4429,7 +4418,7 @@
         </is>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1">
+    <row r="17" spans="1:19">
       <c r="A17" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E004</t>
@@ -4499,7 +4488,7 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1">
+    <row r="18" spans="1:19">
       <c r="A18" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E005</t>
@@ -4569,7 +4558,7 @@
         </is>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1">
+    <row r="19" spans="1:19">
       <c r="A19" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E006</t>
@@ -4639,7 +4628,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1">
+    <row r="20" spans="1:19">
       <c r="A20" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E007</t>
@@ -4709,7 +4698,7 @@
         </is>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1">
+    <row r="21" spans="1:19">
       <c r="A21" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E008</t>
@@ -4779,7 +4768,7 @@
         </is>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1">
+    <row r="22" spans="1:19">
       <c r="A22" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E009</t>
@@ -4849,7 +4838,7 @@
         </is>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1">
+    <row r="23" spans="1:19">
       <c r="A23" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-NT-E010</t>
@@ -4919,7 +4908,7 @@
         </is>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1">
+    <row r="24" spans="1:19">
       <c r="A24" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E001</t>
@@ -4989,7 +4978,7 @@
         </is>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1">
+    <row r="25" spans="1:19">
       <c r="A25" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E002</t>
@@ -5059,7 +5048,7 @@
         </is>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1">
+    <row r="26" spans="1:19">
       <c r="A26" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E003</t>
@@ -5129,7 +5118,7 @@
         </is>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1">
+    <row r="27" spans="1:19">
       <c r="A27" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E004</t>
@@ -5199,7 +5188,7 @@
         </is>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1">
+    <row r="28" spans="1:19">
       <c r="A28" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E005</t>
@@ -5274,7 +5263,7 @@
         </is>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1">
+    <row r="29" spans="1:19">
       <c r="A29" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E006</t>
@@ -5344,7 +5333,7 @@
         </is>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1">
+    <row r="30" spans="1:19">
       <c r="A30" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E007</t>
@@ -5414,7 +5403,7 @@
         </is>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1">
+    <row r="31" spans="1:19">
       <c r="A31" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E008</t>
@@ -5484,7 +5473,7 @@
         </is>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1">
+    <row r="32" spans="1:19">
       <c r="A32" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E009</t>
@@ -5554,7 +5543,7 @@
         </is>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1">
+    <row r="33" spans="1:19">
       <c r="A33" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-NT-E010</t>
@@ -5624,7 +5613,7 @@
         </is>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1">
+    <row r="34" spans="1:19">
       <c r="A34" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E001</t>
@@ -5694,7 +5683,7 @@
         </is>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1">
+    <row r="35" spans="1:19">
       <c r="A35" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E002</t>
@@ -5764,7 +5753,7 @@
         </is>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1">
+    <row r="36" spans="1:19">
       <c r="A36" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E003</t>
@@ -5834,7 +5823,7 @@
         </is>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1">
+    <row r="37" spans="1:19">
       <c r="A37" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E004</t>
@@ -5904,7 +5893,7 @@
         </is>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1">
+    <row r="38" spans="1:19">
       <c r="A38" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E005</t>
@@ -5974,7 +5963,7 @@
         </is>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1">
+    <row r="39" spans="1:19">
       <c r="A39" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E006</t>
@@ -6044,7 +6033,7 @@
         </is>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1">
+    <row r="40" spans="1:19">
       <c r="A40" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E007</t>
@@ -6114,7 +6103,7 @@
         </is>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1">
+    <row r="41" spans="1:19">
       <c r="A41" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E008</t>
@@ -6184,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1">
+    <row r="42" spans="1:19">
       <c r="A42" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E009</t>
@@ -6254,7 +6243,7 @@
         </is>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1">
+    <row r="43" spans="1:19">
       <c r="A43" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-NT-E010</t>
@@ -6324,7 +6313,7 @@
         </is>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1">
+    <row r="44" spans="1:19">
       <c r="A44" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E001</t>
@@ -6393,7 +6382,7 @@
         </is>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1">
+    <row r="45" spans="1:19">
       <c r="A45" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E002</t>
@@ -6463,7 +6452,7 @@
         </is>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1">
+    <row r="46" spans="1:19">
       <c r="A46" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E003</t>
@@ -6532,7 +6521,7 @@
         </is>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1">
+    <row r="47" spans="1:19">
       <c r="A47" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E004</t>
@@ -6602,7 +6591,7 @@
         </is>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1">
+    <row r="48" spans="1:19">
       <c r="A48" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E005</t>
@@ -6672,7 +6661,7 @@
         </is>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1">
+    <row r="49" spans="1:19">
       <c r="A49" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E006</t>
@@ -6742,7 +6731,7 @@
         </is>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1">
+    <row r="50" spans="1:19">
       <c r="A50" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E007</t>
@@ -6812,7 +6801,7 @@
         </is>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1">
+    <row r="51" spans="1:19">
       <c r="A51" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E008</t>
@@ -6882,7 +6871,7 @@
         </is>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1">
+    <row r="52" spans="1:19">
       <c r="A52" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E009</t>
@@ -6957,7 +6946,7 @@
         </is>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1">
+    <row r="53" spans="1:19">
       <c r="A53" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E010</t>
@@ -7027,7 +7016,7 @@
         </is>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1">
+    <row r="54" spans="1:19">
       <c r="A54" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E011</t>
@@ -7100,7 +7089,7 @@
         </is>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1">
+    <row r="55" spans="1:19">
       <c r="A55" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-NT-E012</t>
@@ -7173,7 +7162,7 @@
         </is>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1">
+    <row r="56" spans="1:19">
       <c r="A56" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E001</t>
@@ -7243,7 +7232,7 @@
         </is>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1">
+    <row r="57" spans="1:19">
       <c r="A57" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E002</t>
@@ -7318,7 +7307,7 @@
         </is>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1">
+    <row r="58" spans="1:19">
       <c r="A58" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E003</t>
@@ -7393,7 +7382,7 @@
         </is>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1">
+    <row r="59" spans="1:19">
       <c r="A59" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E004</t>
@@ -7468,7 +7457,7 @@
         </is>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1">
+    <row r="60" spans="1:19">
       <c r="A60" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E005</t>
@@ -7538,7 +7527,7 @@
         </is>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1">
+    <row r="61" spans="1:19">
       <c r="A61" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E006</t>
@@ -7608,7 +7597,7 @@
         </is>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1">
+    <row r="62" spans="1:19">
       <c r="A62" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E007</t>
@@ -7683,7 +7672,7 @@
         </is>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1">
+    <row r="63" spans="1:19">
       <c r="A63" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E008</t>
@@ -7753,7 +7742,7 @@
         </is>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1">
+    <row r="64" spans="1:19">
       <c r="A64" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E009</t>
@@ -7823,7 +7812,7 @@
         </is>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1">
+    <row r="65" spans="1:19">
       <c r="A65" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-NT-E010</t>
@@ -7898,7 +7887,7 @@
         </is>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1">
+    <row r="66" spans="1:19">
       <c r="A66" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E001</t>
@@ -7973,7 +7962,7 @@
         </is>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1">
+    <row r="67" spans="1:19">
       <c r="A67" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E002</t>
@@ -8043,7 +8032,7 @@
         </is>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1">
+    <row r="68" spans="1:19">
       <c r="A68" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E003</t>
@@ -8113,7 +8102,7 @@
         </is>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1">
+    <row r="69" spans="1:19">
       <c r="A69" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E004</t>
@@ -8183,7 +8172,7 @@
         </is>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1">
+    <row r="70" spans="1:19">
       <c r="A70" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E005</t>
@@ -8253,7 +8242,7 @@
         </is>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1">
+    <row r="71" spans="1:19">
       <c r="A71" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E006</t>
@@ -8322,7 +8311,7 @@
         </is>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1">
+    <row r="72" spans="1:19">
       <c r="A72" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E007</t>
@@ -8397,7 +8386,7 @@
         </is>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1">
+    <row r="73" spans="1:19">
       <c r="A73" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E008</t>
@@ -8472,7 +8461,7 @@
         </is>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1">
+    <row r="74" spans="1:19">
       <c r="A74" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E009</t>
@@ -8542,7 +8531,7 @@
         </is>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1">
+    <row r="75" spans="1:19">
       <c r="A75" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E010</t>
@@ -8611,7 +8600,7 @@
         </is>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1">
+    <row r="76" spans="1:19">
       <c r="A76" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E011</t>
@@ -8684,7 +8673,7 @@
         </is>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1">
+    <row r="77" spans="1:19">
       <c r="A77" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-NT-E012</t>
@@ -8757,7 +8746,7 @@
         </is>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1">
+    <row r="78" spans="1:19">
       <c r="A78" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E001</t>
@@ -8827,7 +8816,7 @@
         </is>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1">
+    <row r="79" spans="1:19">
       <c r="A79" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E002</t>
@@ -8897,7 +8886,7 @@
         </is>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1">
+    <row r="80" spans="1:19">
       <c r="A80" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E003</t>
@@ -8967,7 +8956,7 @@
         </is>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1">
+    <row r="81" spans="1:19">
       <c r="A81" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E004</t>
@@ -9036,7 +9025,7 @@
         </is>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1">
+    <row r="82" spans="1:19">
       <c r="A82" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E005</t>
@@ -9106,7 +9095,7 @@
         </is>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1">
+    <row r="83" spans="1:19">
       <c r="A83" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E006</t>
@@ -9176,7 +9165,7 @@
         </is>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1">
+    <row r="84" spans="1:19">
       <c r="A84" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E007</t>
@@ -9245,7 +9234,7 @@
         </is>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1">
+    <row r="85" spans="1:19">
       <c r="A85" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E008</t>
@@ -9315,7 +9304,7 @@
         </is>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1">
+    <row r="86" spans="1:19">
       <c r="A86" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E009</t>
@@ -9385,7 +9374,7 @@
         </is>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1">
+    <row r="87" spans="1:19">
       <c r="A87" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E010</t>
@@ -9455,7 +9444,7 @@
         </is>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1">
+    <row r="88" spans="1:19">
       <c r="A88" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E011</t>
@@ -9528,7 +9517,7 @@
         </is>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1">
+    <row r="89" spans="1:19">
       <c r="A89" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-NT-E012</t>
@@ -9601,7 +9590,7 @@
         </is>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1">
+    <row r="90" spans="1:19">
       <c r="A90" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E001</t>
@@ -9671,7 +9660,7 @@
         </is>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1">
+    <row r="91" spans="1:19">
       <c r="A91" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E002</t>
@@ -9741,7 +9730,7 @@
         </is>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1">
+    <row r="92" spans="1:19">
       <c r="A92" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E003</t>
@@ -9816,7 +9805,7 @@
         </is>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1">
+    <row r="93" spans="1:19">
       <c r="A93" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E004</t>
@@ -9891,7 +9880,7 @@
         </is>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1">
+    <row r="94" spans="1:19">
       <c r="A94" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E005</t>
@@ -9960,7 +9949,7 @@
         </is>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1">
+    <row r="95" spans="1:19">
       <c r="A95" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E006</t>
@@ -10030,7 +10019,7 @@
         </is>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1">
+    <row r="96" spans="1:19">
       <c r="A96" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E007</t>
@@ -10100,7 +10089,7 @@
         </is>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1">
+    <row r="97" spans="1:19">
       <c r="A97" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E008</t>
@@ -10175,7 +10164,7 @@
         </is>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1">
+    <row r="98" spans="1:19">
       <c r="A98" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E009</t>
@@ -10245,7 +10234,7 @@
         </is>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1">
+    <row r="99" spans="1:19">
       <c r="A99" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E010</t>
@@ -10315,7 +10304,7 @@
         </is>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1">
+    <row r="100" spans="1:19">
       <c r="A100" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-NT-E011</t>
@@ -10388,7 +10377,7 @@
         </is>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1">
+    <row r="101" spans="1:19">
       <c r="A101" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E001</t>
@@ -10463,7 +10452,7 @@
         </is>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1">
+    <row r="102" spans="1:19">
       <c r="A102" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E002</t>
@@ -10538,7 +10527,7 @@
         </is>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1">
+    <row r="103" spans="1:19">
       <c r="A103" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E004</t>
@@ -10613,7 +10602,7 @@
         </is>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1">
+    <row r="104" spans="1:19">
       <c r="A104" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E005</t>
@@ -10688,7 +10677,7 @@
         </is>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1">
+    <row r="105" spans="1:19">
       <c r="A105" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E006</t>
@@ -10763,7 +10752,7 @@
         </is>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1">
+    <row r="106" spans="1:19">
       <c r="A106" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E007</t>
@@ -10838,7 +10827,7 @@
         </is>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1">
+    <row r="107" spans="1:19">
       <c r="A107" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E009</t>
@@ -10913,7 +10902,7 @@
         </is>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1">
+    <row r="108" spans="1:19">
       <c r="A108" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E010</t>
@@ -10988,7 +10977,7 @@
         </is>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1">
+    <row r="109" spans="1:19">
       <c r="A109" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E011</t>
@@ -11063,7 +11052,7 @@
         </is>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1">
+    <row r="110" spans="1:19">
       <c r="A110" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E012</t>
@@ -11138,7 +11127,7 @@
         </is>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1">
+    <row r="111" spans="1:19">
       <c r="A111" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E003</t>
@@ -11216,7 +11205,7 @@
         </is>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1">
+    <row r="112" spans="1:19">
       <c r="A112" t="inlineStr">
         <is>
           <t>LOOCV0-P1-S0-T-E008</t>
@@ -11294,7 +11283,7 @@
         </is>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1">
+    <row r="113" spans="1:19">
       <c r="A113" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E001</t>
@@ -11369,7 +11358,7 @@
         </is>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1">
+    <row r="114" spans="1:19">
       <c r="A114" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E002</t>
@@ -11444,7 +11433,7 @@
         </is>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1">
+    <row r="115" spans="1:19">
       <c r="A115" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E003</t>
@@ -11519,7 +11508,7 @@
         </is>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1">
+    <row r="116" spans="1:19">
       <c r="A116" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E004</t>
@@ -11594,7 +11583,7 @@
         </is>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1">
+    <row r="117" spans="1:19">
       <c r="A117" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E005</t>
@@ -11669,7 +11658,7 @@
         </is>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1">
+    <row r="118" spans="1:19">
       <c r="A118" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E006</t>
@@ -11744,7 +11733,7 @@
         </is>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1">
+    <row r="119" spans="1:19">
       <c r="A119" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E007</t>
@@ -11819,7 +11808,7 @@
         </is>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1">
+    <row r="120" spans="1:19">
       <c r="A120" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E008</t>
@@ -11894,7 +11883,7 @@
         </is>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1">
+    <row r="121" spans="1:19">
       <c r="A121" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E009</t>
@@ -11969,7 +11958,7 @@
         </is>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1">
+    <row r="122" spans="1:19">
       <c r="A122" t="inlineStr">
         <is>
           <t>LOOCV0-P2-S0-T-E010</t>
@@ -12044,7 +12033,7 @@
         </is>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1">
+    <row r="123" spans="1:19">
       <c r="A123" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E006</t>
@@ -12114,7 +12103,7 @@
         </is>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1">
+    <row r="124" spans="1:19">
       <c r="A124" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E007</t>
@@ -12184,7 +12173,7 @@
         </is>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1">
+    <row r="125" spans="1:19">
       <c r="A125" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E008</t>
@@ -12254,7 +12243,7 @@
         </is>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1">
+    <row r="126" spans="1:19">
       <c r="A126" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E009</t>
@@ -12324,7 +12313,7 @@
         </is>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1">
+    <row r="127" spans="1:19">
       <c r="A127" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E010</t>
@@ -12394,7 +12383,7 @@
         </is>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1">
+    <row r="128" spans="1:19">
       <c r="A128" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E011</t>
@@ -12464,7 +12453,7 @@
         </is>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1">
+    <row r="129" spans="1:19">
       <c r="A129" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E012</t>
@@ -12534,7 +12523,7 @@
         </is>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1">
+    <row r="130" spans="1:19">
       <c r="A130" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E001</t>
@@ -12603,7 +12592,7 @@
         </is>
       </c>
     </row>
-    <row r="131" spans="1:19" hidden="1">
+    <row r="131" spans="1:19">
       <c r="A131" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E014</t>
@@ -12673,7 +12662,7 @@
         </is>
       </c>
     </row>
-    <row r="132" spans="1:19" hidden="1">
+    <row r="132" spans="1:19">
       <c r="A132" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E015</t>
@@ -12743,7 +12732,7 @@
         </is>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1">
+    <row r="133" spans="1:19">
       <c r="A133" t="inlineStr">
         <is>
           <t>LOOCV0-P3-S0-T-E013</t>
@@ -12821,7 +12810,7 @@
         </is>
       </c>
     </row>
-    <row r="134" spans="1:19" hidden="1">
+    <row r="134" spans="1:19">
       <c r="A134" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E001</t>
@@ -12896,7 +12885,7 @@
         </is>
       </c>
     </row>
-    <row r="135" spans="1:19" hidden="1">
+    <row r="135" spans="1:19">
       <c r="A135" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E002</t>
@@ -12971,7 +12960,7 @@
         </is>
       </c>
     </row>
-    <row r="136" spans="1:19" hidden="1">
+    <row r="136" spans="1:19">
       <c r="A136" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E003</t>
@@ -13046,7 +13035,7 @@
         </is>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1">
+    <row r="137" spans="1:19">
       <c r="A137" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E004</t>
@@ -13121,7 +13110,7 @@
         </is>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1">
+    <row r="138" spans="1:19">
       <c r="A138" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E005</t>
@@ -13196,7 +13185,7 @@
         </is>
       </c>
     </row>
-    <row r="139" spans="1:19" hidden="1">
+    <row r="139" spans="1:19">
       <c r="A139" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E006</t>
@@ -13271,7 +13260,7 @@
         </is>
       </c>
     </row>
-    <row r="140" spans="1:19" hidden="1">
+    <row r="140" spans="1:19">
       <c r="A140" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E007</t>
@@ -13346,7 +13335,7 @@
         </is>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1">
+    <row r="141" spans="1:19">
       <c r="A141" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E008</t>
@@ -13421,7 +13410,7 @@
         </is>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1">
+    <row r="142" spans="1:19">
       <c r="A142" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E009</t>
@@ -13496,7 +13485,7 @@
         </is>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1">
+    <row r="143" spans="1:19">
       <c r="A143" t="inlineStr">
         <is>
           <t>LOOCV0-P4-S0-T-E010</t>
@@ -13571,7 +13560,7 @@
         </is>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1">
+    <row r="144" spans="1:19">
       <c r="A144" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E001</t>
@@ -13646,7 +13635,7 @@
         </is>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1">
+    <row r="145" spans="1:19">
       <c r="A145" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E002</t>
@@ -13721,7 +13710,7 @@
         </is>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1">
+    <row r="146" spans="1:19">
       <c r="A146" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E003</t>
@@ -13796,7 +13785,7 @@
         </is>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1">
+    <row r="147" spans="1:19">
       <c r="A147" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E004</t>
@@ -13871,7 +13860,7 @@
         </is>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1">
+    <row r="148" spans="1:19">
       <c r="A148" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E005</t>
@@ -13946,7 +13935,7 @@
         </is>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1">
+    <row r="149" spans="1:19">
       <c r="A149" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E006</t>
@@ -14021,7 +14010,7 @@
         </is>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1">
+    <row r="150" spans="1:19">
       <c r="A150" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E007</t>
@@ -14096,7 +14085,7 @@
         </is>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1">
+    <row r="151" spans="1:19">
       <c r="A151" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E008</t>
@@ -14171,7 +14160,7 @@
         </is>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1">
+    <row r="152" spans="1:19">
       <c r="A152" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E009</t>
@@ -14246,7 +14235,7 @@
         </is>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1">
+    <row r="153" spans="1:19">
       <c r="A153" t="inlineStr">
         <is>
           <t>LOOCV0-P5-S0-T-E010</t>
@@ -14321,7 +14310,7 @@
         </is>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1">
+    <row r="154" spans="1:19">
       <c r="A154" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E001</t>
@@ -14396,7 +14385,7 @@
         </is>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1">
+    <row r="155" spans="1:19">
       <c r="A155" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E002</t>
@@ -14471,7 +14460,7 @@
         </is>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1">
+    <row r="156" spans="1:19">
       <c r="A156" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E003</t>
@@ -14546,7 +14535,7 @@
         </is>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1">
+    <row r="157" spans="1:19">
       <c r="A157" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E004</t>
@@ -14621,7 +14610,7 @@
         </is>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1">
+    <row r="158" spans="1:19">
       <c r="A158" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E005</t>
@@ -14696,7 +14685,7 @@
         </is>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1">
+    <row r="159" spans="1:19">
       <c r="A159" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E006</t>
@@ -14771,7 +14760,7 @@
         </is>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1">
+    <row r="160" spans="1:19">
       <c r="A160" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E007</t>
@@ -14846,7 +14835,7 @@
         </is>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1">
+    <row r="161" spans="1:19">
       <c r="A161" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E008</t>
@@ -14921,7 +14910,7 @@
         </is>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1">
+    <row r="162" spans="1:19">
       <c r="A162" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E009</t>
@@ -14996,7 +14985,7 @@
         </is>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1">
+    <row r="163" spans="1:19">
       <c r="A163" t="inlineStr">
         <is>
           <t>LOOCV0-P6-S0-T-E010</t>
@@ -15071,7 +15060,7 @@
         </is>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1">
+    <row r="164" spans="1:19">
       <c r="A164" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E001</t>
@@ -15146,7 +15135,7 @@
         </is>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1">
+    <row r="165" spans="1:19">
       <c r="A165" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E002</t>
@@ -15221,7 +15210,7 @@
         </is>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1">
+    <row r="166" spans="1:19">
       <c r="A166" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E003</t>
@@ -15296,7 +15285,7 @@
         </is>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1">
+    <row r="167" spans="1:19">
       <c r="A167" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E004</t>
@@ -15371,7 +15360,7 @@
         </is>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1">
+    <row r="168" spans="1:19">
       <c r="A168" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E005</t>
@@ -15446,7 +15435,7 @@
         </is>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1">
+    <row r="169" spans="1:19">
       <c r="A169" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E006</t>
@@ -15521,7 +15510,7 @@
         </is>
       </c>
     </row>
-    <row r="170" spans="1:19" hidden="1">
+    <row r="170" spans="1:19">
       <c r="A170" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E007</t>
@@ -15596,7 +15585,7 @@
         </is>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1">
+    <row r="171" spans="1:19">
       <c r="A171" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E008</t>
@@ -15671,7 +15660,7 @@
         </is>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1">
+    <row r="172" spans="1:19">
       <c r="A172" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E009</t>
@@ -15746,7 +15735,7 @@
         </is>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1">
+    <row r="173" spans="1:19">
       <c r="A173" t="inlineStr">
         <is>
           <t>LOOCV0-P7-S0-T-E010</t>
@@ -15821,7 +15810,7 @@
         </is>
       </c>
     </row>
-    <row r="174" spans="1:19" hidden="1">
+    <row r="174" spans="1:19">
       <c r="A174" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E001</t>
@@ -15896,7 +15885,7 @@
         </is>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1">
+    <row r="175" spans="1:19">
       <c r="A175" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E002</t>
@@ -15971,7 +15960,7 @@
         </is>
       </c>
     </row>
-    <row r="176" spans="1:19" hidden="1">
+    <row r="176" spans="1:19">
       <c r="A176" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E003</t>
@@ -16046,7 +16035,7 @@
         </is>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1">
+    <row r="177" spans="1:19">
       <c r="A177" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E004</t>
@@ -16121,7 +16110,7 @@
         </is>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1">
+    <row r="178" spans="1:19">
       <c r="A178" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E005</t>
@@ -16196,7 +16185,7 @@
         </is>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1">
+    <row r="179" spans="1:19">
       <c r="A179" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E006</t>
@@ -16271,7 +16260,7 @@
         </is>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1">
+    <row r="180" spans="1:19">
       <c r="A180" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E007</t>
@@ -16346,7 +16335,7 @@
         </is>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1">
+    <row r="181" spans="1:19">
       <c r="A181" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E008</t>
@@ -16421,7 +16410,7 @@
         </is>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1">
+    <row r="182" spans="1:19">
       <c r="A182" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E009</t>
@@ -16496,7 +16485,7 @@
         </is>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1">
+    <row r="183" spans="1:19">
       <c r="A183" t="inlineStr">
         <is>
           <t>LOOCV0-P8-S0-T-E010</t>
@@ -16571,7 +16560,7 @@
         </is>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1">
+    <row r="184" spans="1:19">
       <c r="A184" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E001</t>
@@ -16646,7 +16635,7 @@
         </is>
       </c>
     </row>
-    <row r="185" spans="1:19" hidden="1">
+    <row r="185" spans="1:19">
       <c r="A185" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E002</t>
@@ -16721,7 +16710,7 @@
         </is>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1">
+    <row r="186" spans="1:19">
       <c r="A186" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E003</t>
@@ -16796,7 +16785,7 @@
         </is>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1">
+    <row r="187" spans="1:19">
       <c r="A187" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E004</t>
@@ -16871,7 +16860,7 @@
         </is>
       </c>
     </row>
-    <row r="188" spans="1:19" hidden="1">
+    <row r="188" spans="1:19">
       <c r="A188" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E005</t>
@@ -16946,7 +16935,7 @@
         </is>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1">
+    <row r="189" spans="1:19">
       <c r="A189" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E006</t>
@@ -17021,7 +17010,7 @@
         </is>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1">
+    <row r="190" spans="1:19">
       <c r="A190" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E007</t>
@@ -17096,7 +17085,7 @@
         </is>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1">
+    <row r="191" spans="1:19">
       <c r="A191" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E008</t>
@@ -17171,7 +17160,7 @@
         </is>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1">
+    <row r="192" spans="1:19">
       <c r="A192" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E009</t>
@@ -17246,7 +17235,7 @@
         </is>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1">
+    <row r="193" spans="1:19">
       <c r="A193" t="inlineStr">
         <is>
           <t>LOOCV0-P9-S0-T-E010</t>
@@ -17321,7 +17310,7 @@
         </is>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1">
+    <row r="194" spans="1:19">
       <c r="A194" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E001</t>
@@ -17396,7 +17385,7 @@
         </is>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1">
+    <row r="195" spans="1:19">
       <c r="A195" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E002</t>
@@ -17471,7 +17460,7 @@
         </is>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1">
+    <row r="196" spans="1:19">
       <c r="A196" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E003</t>
@@ -17546,7 +17535,7 @@
         </is>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1">
+    <row r="197" spans="1:19">
       <c r="A197" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E004</t>
@@ -17621,7 +17610,7 @@
         </is>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1">
+    <row r="198" spans="1:19">
       <c r="A198" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E005</t>
@@ -17696,7 +17685,7 @@
         </is>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1">
+    <row r="199" spans="1:19">
       <c r="A199" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E006</t>
@@ -17771,7 +17760,7 @@
         </is>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1">
+    <row r="200" spans="1:19">
       <c r="A200" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E007</t>
@@ -17846,7 +17835,7 @@
         </is>
       </c>
     </row>
-    <row r="201" spans="1:19" hidden="1">
+    <row r="201" spans="1:19">
       <c r="A201" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E008</t>
@@ -17921,7 +17910,7 @@
         </is>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1">
+    <row r="202" spans="1:19">
       <c r="A202" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E009</t>
@@ -17996,7 +17985,7 @@
         </is>
       </c>
     </row>
-    <row r="203" spans="1:19" hidden="1">
+    <row r="203" spans="1:19">
       <c r="A203" t="inlineStr">
         <is>
           <t>LOOCV1-P1-S0-T-E010</t>
@@ -18071,7 +18060,7 @@
         </is>
       </c>
     </row>
-    <row r="204" spans="1:19" hidden="1">
+    <row r="204" spans="1:19">
       <c r="A204" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E001</t>
@@ -18146,7 +18135,7 @@
         </is>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1">
+    <row r="205" spans="1:19">
       <c r="A205" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E002</t>
@@ -18221,7 +18210,7 @@
         </is>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1">
+    <row r="206" spans="1:19">
       <c r="A206" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E003</t>
@@ -18296,7 +18285,7 @@
         </is>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1">
+    <row r="207" spans="1:19">
       <c r="A207" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E004</t>
@@ -18371,7 +18360,7 @@
         </is>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1">
+    <row r="208" spans="1:19">
       <c r="A208" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E005</t>
@@ -18446,7 +18435,7 @@
         </is>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1">
+    <row r="209" spans="1:19">
       <c r="A209" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E006</t>
@@ -18521,7 +18510,7 @@
         </is>
       </c>
     </row>
-    <row r="210" spans="1:19" hidden="1">
+    <row r="210" spans="1:19">
       <c r="A210" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E007</t>
@@ -18596,7 +18585,7 @@
         </is>
       </c>
     </row>
-    <row r="211" spans="1:19" hidden="1">
+    <row r="211" spans="1:19">
       <c r="A211" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E008</t>
@@ -18671,7 +18660,7 @@
         </is>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1">
+    <row r="212" spans="1:19">
       <c r="A212" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E009</t>
@@ -18746,7 +18735,7 @@
         </is>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1">
+    <row r="213" spans="1:19">
       <c r="A213" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E010</t>
@@ -18821,7 +18810,7 @@
         </is>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1">
+    <row r="214" spans="1:19">
       <c r="A214" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E011</t>
@@ -18899,7 +18888,7 @@
         </is>
       </c>
     </row>
-    <row r="215" spans="1:19" hidden="1">
+    <row r="215" spans="1:19">
       <c r="A215" t="inlineStr">
         <is>
           <t>LOOCV1-P1A-S0-T-E012</t>
@@ -18977,7 +18966,7 @@
         </is>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1">
+    <row r="216" spans="1:19">
       <c r="A216" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E001</t>
@@ -19052,7 +19041,7 @@
         </is>
       </c>
     </row>
-    <row r="217" spans="1:19" hidden="1">
+    <row r="217" spans="1:19">
       <c r="A217" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E002</t>
@@ -19127,7 +19116,7 @@
         </is>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1">
+    <row r="218" spans="1:19">
       <c r="A218" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E003</t>
@@ -19202,7 +19191,7 @@
         </is>
       </c>
     </row>
-    <row r="219" spans="1:19" hidden="1">
+    <row r="219" spans="1:19">
       <c r="A219" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E004</t>
@@ -19277,7 +19266,7 @@
         </is>
       </c>
     </row>
-    <row r="220" spans="1:19" hidden="1">
+    <row r="220" spans="1:19">
       <c r="A220" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E005</t>
@@ -19352,7 +19341,7 @@
         </is>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1">
+    <row r="221" spans="1:19">
       <c r="A221" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E006</t>
@@ -19427,7 +19416,7 @@
         </is>
       </c>
     </row>
-    <row r="222" spans="1:19" hidden="1">
+    <row r="222" spans="1:19">
       <c r="A222" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E007</t>
@@ -19502,7 +19491,7 @@
         </is>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1">
+    <row r="223" spans="1:19">
       <c r="A223" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E008</t>
@@ -19577,7 +19566,7 @@
         </is>
       </c>
     </row>
-    <row r="224" spans="1:19" hidden="1">
+    <row r="224" spans="1:19">
       <c r="A224" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E009</t>
@@ -19652,7 +19641,7 @@
         </is>
       </c>
     </row>
-    <row r="225" spans="1:19" hidden="1">
+    <row r="225" spans="1:19">
       <c r="A225" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E010</t>
@@ -19727,7 +19716,7 @@
         </is>
       </c>
     </row>
-    <row r="226" spans="1:19" hidden="1">
+    <row r="226" spans="1:19">
       <c r="A226" t="inlineStr">
         <is>
           <t>LOOCV1-P2-S0-T-E011</t>
@@ -19805,7 +19794,7 @@
         </is>
       </c>
     </row>
-    <row r="227" spans="1:19" hidden="1">
+    <row r="227" spans="1:19">
       <c r="A227" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E001</t>
@@ -19880,7 +19869,7 @@
         </is>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1">
+    <row r="228" spans="1:19">
       <c r="A228" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E002</t>
@@ -19955,7 +19944,7 @@
         </is>
       </c>
     </row>
-    <row r="229" spans="1:19" hidden="1">
+    <row r="229" spans="1:19">
       <c r="A229" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E003</t>
@@ -20030,7 +20019,7 @@
         </is>
       </c>
     </row>
-    <row r="230" spans="1:19" hidden="1">
+    <row r="230" spans="1:19">
       <c r="A230" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E004</t>
@@ -20105,7 +20094,7 @@
         </is>
       </c>
     </row>
-    <row r="231" spans="1:19" hidden="1">
+    <row r="231" spans="1:19">
       <c r="A231" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E005</t>
@@ -20180,7 +20169,7 @@
         </is>
       </c>
     </row>
-    <row r="232" spans="1:19" hidden="1">
+    <row r="232" spans="1:19">
       <c r="A232" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E006</t>
@@ -20255,7 +20244,7 @@
         </is>
       </c>
     </row>
-    <row r="233" spans="1:19" hidden="1">
+    <row r="233" spans="1:19">
       <c r="A233" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E007</t>
@@ -20330,7 +20319,7 @@
         </is>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1">
+    <row r="234" spans="1:19">
       <c r="A234" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E008</t>
@@ -20405,7 +20394,7 @@
         </is>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1">
+    <row r="235" spans="1:19">
       <c r="A235" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E009</t>
@@ -20480,7 +20469,7 @@
         </is>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1">
+    <row r="236" spans="1:19">
       <c r="A236" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E010</t>
@@ -20555,7 +20544,7 @@
         </is>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1">
+    <row r="237" spans="1:19">
       <c r="A237" t="inlineStr">
         <is>
           <t>LOOCV1-P3-S0-T-E011</t>
@@ -20633,7 +20622,7 @@
         </is>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1">
+    <row r="238" spans="1:19">
       <c r="A238" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E001</t>
@@ -20708,7 +20697,7 @@
         </is>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1">
+    <row r="239" spans="1:19">
       <c r="A239" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E002</t>
@@ -20783,7 +20772,7 @@
         </is>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1">
+    <row r="240" spans="1:19">
       <c r="A240" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E003</t>
@@ -20858,7 +20847,7 @@
         </is>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1">
+    <row r="241" spans="1:19">
       <c r="A241" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E004</t>
@@ -20933,7 +20922,7 @@
         </is>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1">
+    <row r="242" spans="1:19">
       <c r="A242" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E005</t>
@@ -21008,7 +20997,7 @@
         </is>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1">
+    <row r="243" spans="1:19">
       <c r="A243" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E006</t>
@@ -21083,7 +21072,7 @@
         </is>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1">
+    <row r="244" spans="1:19">
       <c r="A244" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E007</t>
@@ -21158,7 +21147,7 @@
         </is>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1">
+    <row r="245" spans="1:19">
       <c r="A245" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E008</t>
@@ -21233,7 +21222,7 @@
         </is>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1">
+    <row r="246" spans="1:19">
       <c r="A246" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E009</t>
@@ -21308,7 +21297,7 @@
         </is>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1">
+    <row r="247" spans="1:19">
       <c r="A247" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E010</t>
@@ -21383,7 +21372,7 @@
         </is>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1">
+    <row r="248" spans="1:19">
       <c r="A248" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E011</t>
@@ -21461,7 +21450,7 @@
         </is>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1">
+    <row r="249" spans="1:19">
       <c r="A249" t="inlineStr">
         <is>
           <t>LOOCV1-P5-S0-T-E012</t>
@@ -21539,7 +21528,7 @@
         </is>
       </c>
     </row>
-    <row r="250" spans="1:19" hidden="1">
+    <row r="250" spans="1:19">
       <c r="A250" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E001</t>
@@ -21614,7 +21603,7 @@
         </is>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1">
+    <row r="251" spans="1:19">
       <c r="A251" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E002</t>
@@ -21689,7 +21678,7 @@
         </is>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1">
+    <row r="252" spans="1:19">
       <c r="A252" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E003</t>
@@ -21764,7 +21753,7 @@
         </is>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1">
+    <row r="253" spans="1:19">
       <c r="A253" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E004</t>
@@ -21839,7 +21828,7 @@
         </is>
       </c>
     </row>
-    <row r="254" spans="1:19" hidden="1">
+    <row r="254" spans="1:19">
       <c r="A254" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E005</t>
@@ -21914,7 +21903,7 @@
         </is>
       </c>
     </row>
-    <row r="255" spans="1:19" hidden="1">
+    <row r="255" spans="1:19">
       <c r="A255" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E006</t>
@@ -21989,7 +21978,7 @@
         </is>
       </c>
     </row>
-    <row r="256" spans="1:19" hidden="1">
+    <row r="256" spans="1:19">
       <c r="A256" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E007</t>
@@ -22064,7 +22053,7 @@
         </is>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1">
+    <row r="257" spans="1:19">
       <c r="A257" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E008</t>
@@ -22139,7 +22128,7 @@
         </is>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1">
+    <row r="258" spans="1:19">
       <c r="A258" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E009</t>
@@ -22214,7 +22203,7 @@
         </is>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1">
+    <row r="259" spans="1:19">
       <c r="A259" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E010</t>
@@ -22289,7 +22278,7 @@
         </is>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1">
+    <row r="260" spans="1:19">
       <c r="A260" t="inlineStr">
         <is>
           <t>LOOCV1-P6-S0-T-E011</t>
@@ -22367,7 +22356,7 @@
         </is>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1">
+    <row r="261" spans="1:19">
       <c r="A261" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E001</t>
@@ -22442,7 +22431,7 @@
         </is>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1">
+    <row r="262" spans="1:19">
       <c r="A262" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E002</t>
@@ -22517,7 +22506,7 @@
         </is>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1">
+    <row r="263" spans="1:19">
       <c r="A263" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E003</t>
@@ -22592,7 +22581,7 @@
         </is>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1">
+    <row r="264" spans="1:19">
       <c r="A264" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E004</t>
@@ -22667,7 +22656,7 @@
         </is>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1">
+    <row r="265" spans="1:19">
       <c r="A265" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E005</t>
@@ -22742,7 +22731,7 @@
         </is>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1">
+    <row r="266" spans="1:19">
       <c r="A266" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E006</t>
@@ -22817,7 +22806,7 @@
         </is>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1">
+    <row r="267" spans="1:19">
       <c r="A267" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E007</t>
@@ -22892,7 +22881,7 @@
         </is>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1">
+    <row r="268" spans="1:19">
       <c r="A268" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E008</t>
@@ -22967,7 +22956,7 @@
         </is>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1">
+    <row r="269" spans="1:19">
       <c r="A269" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E009</t>
@@ -23042,7 +23031,7 @@
         </is>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1">
+    <row r="270" spans="1:19">
       <c r="A270" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E010</t>
@@ -23117,7 +23106,7 @@
         </is>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1">
+    <row r="271" spans="1:19">
       <c r="A271" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E011</t>
@@ -23195,7 +23184,7 @@
         </is>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1">
+    <row r="272" spans="1:19">
       <c r="A272" t="inlineStr">
         <is>
           <t>LOOCV1-P7-S0-T-E012</t>
@@ -23273,7 +23262,7 @@
         </is>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1">
+    <row r="273" spans="1:19">
       <c r="A273" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E001</t>
@@ -23348,7 +23337,7 @@
         </is>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1">
+    <row r="274" spans="1:19">
       <c r="A274" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E002</t>
@@ -23423,7 +23412,7 @@
         </is>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1">
+    <row r="275" spans="1:19">
       <c r="A275" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E003</t>
@@ -23498,7 +23487,7 @@
         </is>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1">
+    <row r="276" spans="1:19">
       <c r="A276" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E004</t>
@@ -23573,7 +23562,7 @@
         </is>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1">
+    <row r="277" spans="1:19">
       <c r="A277" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E005</t>
@@ -23648,7 +23637,7 @@
         </is>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1">
+    <row r="278" spans="1:19">
       <c r="A278" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E006</t>
@@ -23723,7 +23712,7 @@
         </is>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1">
+    <row r="279" spans="1:19">
       <c r="A279" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E007</t>
@@ -23798,7 +23787,7 @@
         </is>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1">
+    <row r="280" spans="1:19">
       <c r="A280" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E008</t>
@@ -23873,7 +23862,7 @@
         </is>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1">
+    <row r="281" spans="1:19">
       <c r="A281" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E009</t>
@@ -23948,7 +23937,7 @@
         </is>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1">
+    <row r="282" spans="1:19">
       <c r="A282" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E010</t>
@@ -24023,7 +24012,7 @@
         </is>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1">
+    <row r="283" spans="1:19">
       <c r="A283" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E011</t>
@@ -24101,7 +24090,7 @@
         </is>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1">
+    <row r="284" spans="1:19">
       <c r="A284" t="inlineStr">
         <is>
           <t>LOOCV1-P8-S0-T-E012</t>
@@ -24179,7 +24168,7 @@
         </is>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1">
+    <row r="285" spans="1:19">
       <c r="A285" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E001</t>
@@ -24254,7 +24243,7 @@
         </is>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1">
+    <row r="286" spans="1:19">
       <c r="A286" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E002</t>
@@ -24329,7 +24318,7 @@
         </is>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1">
+    <row r="287" spans="1:19">
       <c r="A287" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E003</t>
@@ -24404,7 +24393,7 @@
         </is>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1">
+    <row r="288" spans="1:19">
       <c r="A288" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E004</t>
@@ -24479,7 +24468,7 @@
         </is>
       </c>
     </row>
-    <row r="289" spans="1:19" hidden="1">
+    <row r="289" spans="1:19">
       <c r="A289" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E005</t>
@@ -24554,7 +24543,7 @@
         </is>
       </c>
     </row>
-    <row r="290" spans="1:19" hidden="1">
+    <row r="290" spans="1:19">
       <c r="A290" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E006</t>
@@ -24629,7 +24618,7 @@
         </is>
       </c>
     </row>
-    <row r="291" spans="1:19" hidden="1">
+    <row r="291" spans="1:19">
       <c r="A291" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E007</t>
@@ -24704,7 +24693,7 @@
         </is>
       </c>
     </row>
-    <row r="292" spans="1:19" hidden="1">
+    <row r="292" spans="1:19">
       <c r="A292" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E008</t>
@@ -24779,7 +24768,7 @@
         </is>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1">
+    <row r="293" spans="1:19">
       <c r="A293" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E009</t>
@@ -24854,7 +24843,7 @@
         </is>
       </c>
     </row>
-    <row r="294" spans="1:19" hidden="1">
+    <row r="294" spans="1:19">
       <c r="A294" t="inlineStr">
         <is>
           <t>LOOCV1-P9-S0-T-E010</t>
@@ -24929,7 +24918,7 @@
         </is>
       </c>
     </row>
-    <row r="295" spans="1:19" hidden="1">
+    <row r="295" spans="1:19">
       <c r="A295" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E001</t>
@@ -25075,7 +25064,7 @@
         </is>
       </c>
     </row>
-    <row r="297" spans="1:19" s="59" customFormat="1" ht="21.75" hidden="1" customHeight="1">
+    <row r="297" spans="1:19" s="59" customFormat="1" ht="21.75" customHeight="1">
       <c r="A297" s="59" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E003</t>
@@ -25221,7 +25210,7 @@
         </is>
       </c>
     </row>
-    <row r="299" spans="1:19" hidden="1">
+    <row r="299" spans="1:19">
       <c r="A299" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E005</t>
@@ -25291,7 +25280,7 @@
         </is>
       </c>
     </row>
-    <row r="300" spans="1:19" hidden="1">
+    <row r="300" spans="1:19">
       <c r="A300" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E006</t>
@@ -25513,7 +25502,7 @@
         </is>
       </c>
     </row>
-    <row r="303" spans="1:19" hidden="1">
+    <row r="303" spans="1:19">
       <c r="A303" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E009</t>
@@ -25738,7 +25727,7 @@
         </is>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1">
+    <row r="306" spans="1:19">
       <c r="A306" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E012</t>
@@ -25816,7 +25805,7 @@
         </is>
       </c>
     </row>
-    <row r="307" spans="1:19" hidden="1">
+    <row r="307" spans="1:19">
       <c r="A307" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E013</t>
@@ -25894,7 +25883,7 @@
         </is>
       </c>
     </row>
-    <row r="308" spans="1:19" hidden="1">
+    <row r="308" spans="1:19">
       <c r="A308" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E014</t>
@@ -25972,7 +25961,7 @@
         </is>
       </c>
     </row>
-    <row r="309" spans="1:19" hidden="1">
+    <row r="309" spans="1:19">
       <c r="A309" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E015</t>
@@ -26124,7 +26113,7 @@
         </is>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1">
+    <row r="311" spans="1:19">
       <c r="A311" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-NT-E017</t>
@@ -26202,7 +26191,7 @@
         </is>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1">
+    <row r="312" spans="1:19">
       <c r="A312" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E001</t>
@@ -26353,7 +26342,7 @@
         </is>
       </c>
     </row>
-    <row r="314" spans="1:19" hidden="1">
+    <row r="314" spans="1:19">
       <c r="A314" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E003</t>
@@ -26428,7 +26417,7 @@
         </is>
       </c>
     </row>
-    <row r="315" spans="1:19" hidden="1">
+    <row r="315" spans="1:19">
       <c r="A315" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E004</t>
@@ -26574,7 +26563,7 @@
         </is>
       </c>
     </row>
-    <row r="317" spans="1:19" hidden="1">
+    <row r="317" spans="1:19">
       <c r="A317" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E006</t>
@@ -26649,7 +26638,7 @@
         </is>
       </c>
     </row>
-    <row r="318" spans="1:19" hidden="1">
+    <row r="318" spans="1:19">
       <c r="A318" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E007</t>
@@ -26724,7 +26713,7 @@
         </is>
       </c>
     </row>
-    <row r="319" spans="1:19" hidden="1">
+    <row r="319" spans="1:19">
       <c r="A319" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E008</t>
@@ -26799,7 +26788,7 @@
         </is>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1">
+    <row r="320" spans="1:19">
       <c r="A320" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E009</t>
@@ -26869,7 +26858,7 @@
         </is>
       </c>
     </row>
-    <row r="321" spans="1:19" hidden="1">
+    <row r="321" spans="1:19">
       <c r="A321" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E010</t>
@@ -26944,7 +26933,7 @@
         </is>
       </c>
     </row>
-    <row r="322" spans="1:19" hidden="1">
+    <row r="322" spans="1:19">
       <c r="A322" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E011</t>
@@ -27101,7 +27090,7 @@
         </is>
       </c>
     </row>
-    <row r="324" spans="1:19" hidden="1">
+    <row r="324" spans="1:19">
       <c r="A324" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-NT-E013</t>
@@ -27179,7 +27168,7 @@
         </is>
       </c>
     </row>
-    <row r="325" spans="1:19" hidden="1">
+    <row r="325" spans="1:19">
       <c r="A325" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E001</t>
@@ -27249,7 +27238,7 @@
         </is>
       </c>
     </row>
-    <row r="326" spans="1:19" hidden="1">
+    <row r="326" spans="1:19">
       <c r="A326" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E002</t>
@@ -27319,7 +27308,7 @@
         </is>
       </c>
     </row>
-    <row r="327" spans="1:19" hidden="1">
+    <row r="327" spans="1:19">
       <c r="A327" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E003</t>
@@ -27465,7 +27454,7 @@
         </is>
       </c>
     </row>
-    <row r="329" spans="1:19" hidden="1">
+    <row r="329" spans="1:19">
       <c r="A329" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E005</t>
@@ -27768,7 +27757,7 @@
         </is>
       </c>
     </row>
-    <row r="333" spans="1:19" hidden="1">
+    <row r="333" spans="1:19">
       <c r="A333" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E009</t>
@@ -27919,7 +27908,7 @@
         </is>
       </c>
     </row>
-    <row r="335" spans="1:19" hidden="1">
+    <row r="335" spans="1:19">
       <c r="A335" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E011</t>
@@ -28313,7 +28302,7 @@
         </is>
       </c>
     </row>
-    <row r="340" spans="1:19" hidden="1">
+    <row r="340" spans="1:19">
       <c r="A340" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E016</t>
@@ -28549,7 +28538,7 @@
         </is>
       </c>
     </row>
-    <row r="343" spans="1:19" hidden="1">
+    <row r="343" spans="1:19">
       <c r="A343" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E019</t>
@@ -28627,7 +28616,7 @@
         </is>
       </c>
     </row>
-    <row r="344" spans="1:19" hidden="1">
+    <row r="344" spans="1:19">
       <c r="A344" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E020</t>
@@ -28705,7 +28694,7 @@
         </is>
       </c>
     </row>
-    <row r="345" spans="1:19" hidden="1">
+    <row r="345" spans="1:19">
       <c r="A345" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-NT-E021</t>
@@ -28783,7 +28772,7 @@
         </is>
       </c>
     </row>
-    <row r="346" spans="1:19" hidden="1">
+    <row r="346" spans="1:19">
       <c r="A346" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E001</t>
@@ -28929,7 +28918,7 @@
         </is>
       </c>
     </row>
-    <row r="348" spans="1:19" hidden="1">
+    <row r="348" spans="1:19">
       <c r="A348" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E003</t>
@@ -29075,7 +29064,7 @@
         </is>
       </c>
     </row>
-    <row r="350" spans="1:19" hidden="1">
+    <row r="350" spans="1:19">
       <c r="A350" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E005</t>
@@ -29217,7 +29206,7 @@
         </is>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1">
+    <row r="352" spans="1:19">
       <c r="A352" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E007</t>
@@ -29287,7 +29276,7 @@
         </is>
       </c>
     </row>
-    <row r="353" spans="1:19" hidden="1">
+    <row r="353" spans="1:19">
       <c r="A353" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E008</t>
@@ -29357,7 +29346,7 @@
         </is>
       </c>
     </row>
-    <row r="354" spans="1:19" hidden="1">
+    <row r="354" spans="1:19">
       <c r="A354" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E009</t>
@@ -29427,7 +29416,7 @@
         </is>
       </c>
     </row>
-    <row r="355" spans="1:19" hidden="1">
+    <row r="355" spans="1:19">
       <c r="A355" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E010</t>
@@ -29497,7 +29486,7 @@
         </is>
       </c>
     </row>
-    <row r="356" spans="1:19" hidden="1">
+    <row r="356" spans="1:19">
       <c r="A356" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E011</t>
@@ -29575,7 +29564,7 @@
         </is>
       </c>
     </row>
-    <row r="357" spans="1:19" hidden="1">
+    <row r="357" spans="1:19">
       <c r="A357" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E012</t>
@@ -29653,7 +29642,7 @@
         </is>
       </c>
     </row>
-    <row r="358" spans="1:19" hidden="1">
+    <row r="358" spans="1:19">
       <c r="A358" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-NT-E013</t>
@@ -29731,7 +29720,7 @@
         </is>
       </c>
     </row>
-    <row r="359" spans="1:19" hidden="1">
+    <row r="359" spans="1:19">
       <c r="A359" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E001</t>
@@ -29801,7 +29790,7 @@
         </is>
       </c>
     </row>
-    <row r="360" spans="1:19" hidden="1">
+    <row r="360" spans="1:19">
       <c r="A360" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E002</t>
@@ -29871,7 +29860,7 @@
         </is>
       </c>
     </row>
-    <row r="361" spans="1:19" hidden="1">
+    <row r="361" spans="1:19">
       <c r="A361" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E003</t>
@@ -29941,7 +29930,7 @@
         </is>
       </c>
     </row>
-    <row r="362" spans="1:19" hidden="1">
+    <row r="362" spans="1:19">
       <c r="A362" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E004</t>
@@ -30011,7 +30000,7 @@
         </is>
       </c>
     </row>
-    <row r="363" spans="1:19" hidden="1">
+    <row r="363" spans="1:19">
       <c r="A363" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E005</t>
@@ -30086,7 +30075,7 @@
         </is>
       </c>
     </row>
-    <row r="364" spans="1:19" hidden="1">
+    <row r="364" spans="1:19">
       <c r="A364" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E006</t>
@@ -30232,7 +30221,7 @@
         </is>
       </c>
     </row>
-    <row r="366" spans="1:19" hidden="1">
+    <row r="366" spans="1:19">
       <c r="A366" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E008</t>
@@ -30307,7 +30296,7 @@
         </is>
       </c>
     </row>
-    <row r="367" spans="1:19" hidden="1">
+    <row r="367" spans="1:19">
       <c r="A367" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E009</t>
@@ -30377,7 +30366,7 @@
         </is>
       </c>
     </row>
-    <row r="368" spans="1:19" hidden="1">
+    <row r="368" spans="1:19">
       <c r="A368" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E010</t>
@@ -30447,7 +30436,7 @@
         </is>
       </c>
     </row>
-    <row r="369" spans="1:19" hidden="1">
+    <row r="369" spans="1:19">
       <c r="A369" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-NT-E011</t>
@@ -30525,7 +30514,7 @@
         </is>
       </c>
     </row>
-    <row r="370" spans="1:19" hidden="1">
+    <row r="370" spans="1:19">
       <c r="A370" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E001</t>
@@ -30671,7 +30660,7 @@
         </is>
       </c>
     </row>
-    <row r="372" spans="1:19" hidden="1">
+    <row r="372" spans="1:19">
       <c r="A372" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E003</t>
@@ -30746,7 +30735,7 @@
         </is>
       </c>
     </row>
-    <row r="373" spans="1:19" hidden="1">
+    <row r="373" spans="1:19">
       <c r="A373" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E004</t>
@@ -30816,7 +30805,7 @@
         </is>
       </c>
     </row>
-    <row r="374" spans="1:19" hidden="1">
+    <row r="374" spans="1:19">
       <c r="A374" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E005</t>
@@ -30886,7 +30875,7 @@
         </is>
       </c>
     </row>
-    <row r="375" spans="1:19" hidden="1">
+    <row r="375" spans="1:19">
       <c r="A375" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E006</t>
@@ -30956,7 +30945,7 @@
         </is>
       </c>
     </row>
-    <row r="376" spans="1:19" hidden="1">
+    <row r="376" spans="1:19">
       <c r="A376" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E007</t>
@@ -31031,7 +31020,7 @@
         </is>
       </c>
     </row>
-    <row r="377" spans="1:19" hidden="1">
+    <row r="377" spans="1:19">
       <c r="A377" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E008</t>
@@ -31177,7 +31166,7 @@
         </is>
       </c>
     </row>
-    <row r="379" spans="1:19" hidden="1">
+    <row r="379" spans="1:19">
       <c r="A379" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E010</t>
@@ -31247,7 +31236,7 @@
         </is>
       </c>
     </row>
-    <row r="380" spans="1:19" hidden="1">
+    <row r="380" spans="1:19">
       <c r="A380" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E011</t>
@@ -31404,7 +31393,7 @@
         </is>
       </c>
     </row>
-    <row r="382" spans="1:19" hidden="1">
+    <row r="382" spans="1:19">
       <c r="A382" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-NT-E013</t>
@@ -31482,7 +31471,7 @@
         </is>
       </c>
     </row>
-    <row r="383" spans="1:19" hidden="1">
+    <row r="383" spans="1:19">
       <c r="A383" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E001</t>
@@ -31552,7 +31541,7 @@
         </is>
       </c>
     </row>
-    <row r="384" spans="1:19" hidden="1">
+    <row r="384" spans="1:19">
       <c r="A384" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E002</t>
@@ -31622,7 +31611,7 @@
         </is>
       </c>
     </row>
-    <row r="385" spans="1:19" hidden="1">
+    <row r="385" spans="1:19">
       <c r="A385" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E003</t>
@@ -31692,7 +31681,7 @@
         </is>
       </c>
     </row>
-    <row r="386" spans="1:19" hidden="1">
+    <row r="386" spans="1:19">
       <c r="A386" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E004</t>
@@ -31762,7 +31751,7 @@
         </is>
       </c>
     </row>
-    <row r="387" spans="1:19" hidden="1">
+    <row r="387" spans="1:19">
       <c r="A387" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E005</t>
@@ -31832,7 +31821,7 @@
         </is>
       </c>
     </row>
-    <row r="388" spans="1:19" hidden="1">
+    <row r="388" spans="1:19">
       <c r="A388" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E006</t>
@@ -31907,7 +31896,7 @@
         </is>
       </c>
     </row>
-    <row r="389" spans="1:19" hidden="1">
+    <row r="389" spans="1:19">
       <c r="A389" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E007</t>
@@ -31982,7 +31971,7 @@
         </is>
       </c>
     </row>
-    <row r="390" spans="1:19" hidden="1">
+    <row r="390" spans="1:19">
       <c r="A390" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E008</t>
@@ -32128,7 +32117,7 @@
         </is>
       </c>
     </row>
-    <row r="392" spans="1:19" hidden="1">
+    <row r="392" spans="1:19">
       <c r="A392" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E010</t>
@@ -32203,7 +32192,7 @@
         </is>
       </c>
     </row>
-    <row r="393" spans="1:19" hidden="1">
+    <row r="393" spans="1:19">
       <c r="A393" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-NT-E011</t>
@@ -32281,7 +32270,7 @@
         </is>
       </c>
     </row>
-    <row r="394" spans="1:19" hidden="1">
+    <row r="394" spans="1:19">
       <c r="A394" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E001</t>
@@ -32503,7 +32492,7 @@
         </is>
       </c>
     </row>
-    <row r="397" spans="1:19" hidden="1">
+    <row r="397" spans="1:19">
       <c r="A397" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E004</t>
@@ -32573,7 +32562,7 @@
         </is>
       </c>
     </row>
-    <row r="398" spans="1:19" hidden="1">
+    <row r="398" spans="1:19">
       <c r="A398" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E005</t>
@@ -32643,7 +32632,7 @@
         </is>
       </c>
     </row>
-    <row r="399" spans="1:19" hidden="1">
+    <row r="399" spans="1:19">
       <c r="A399" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E006</t>
@@ -32713,7 +32702,7 @@
         </is>
       </c>
     </row>
-    <row r="400" spans="1:19" hidden="1">
+    <row r="400" spans="1:19">
       <c r="A400" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E007</t>
@@ -32788,7 +32777,7 @@
         </is>
       </c>
     </row>
-    <row r="401" spans="1:19" hidden="1">
+    <row r="401" spans="1:19">
       <c r="A401" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E008</t>
@@ -32858,7 +32847,7 @@
         </is>
       </c>
     </row>
-    <row r="402" spans="1:19" hidden="1">
+    <row r="402" spans="1:19">
       <c r="A402" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E009</t>
@@ -32928,7 +32917,7 @@
         </is>
       </c>
     </row>
-    <row r="403" spans="1:19" hidden="1">
+    <row r="403" spans="1:19">
       <c r="A403" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E010</t>
@@ -33003,7 +32992,7 @@
         </is>
       </c>
     </row>
-    <row r="404" spans="1:19" hidden="1">
+    <row r="404" spans="1:19">
       <c r="A404" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E011</t>
@@ -33081,7 +33070,7 @@
         </is>
       </c>
     </row>
-    <row r="405" spans="1:19" hidden="1">
+    <row r="405" spans="1:19">
       <c r="A405" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-NT-E012</t>
@@ -33159,7 +33148,7 @@
         </is>
       </c>
     </row>
-    <row r="406" spans="1:19" hidden="1">
+    <row r="406" spans="1:19">
       <c r="A406" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E001</t>
@@ -33229,7 +33218,7 @@
         </is>
       </c>
     </row>
-    <row r="407" spans="1:19" hidden="1">
+    <row r="407" spans="1:19">
       <c r="A407" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E002</t>
@@ -33299,7 +33288,7 @@
         </is>
       </c>
     </row>
-    <row r="408" spans="1:19" hidden="1">
+    <row r="408" spans="1:19">
       <c r="A408" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E003</t>
@@ -33369,7 +33358,7 @@
         </is>
       </c>
     </row>
-    <row r="409" spans="1:19" hidden="1">
+    <row r="409" spans="1:19">
       <c r="A409" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E004</t>
@@ -33439,7 +33428,7 @@
         </is>
       </c>
     </row>
-    <row r="410" spans="1:19" hidden="1">
+    <row r="410" spans="1:19">
       <c r="A410" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E005</t>
@@ -33509,7 +33498,7 @@
         </is>
       </c>
     </row>
-    <row r="411" spans="1:19" hidden="1">
+    <row r="411" spans="1:19">
       <c r="A411" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E006</t>
@@ -33579,7 +33568,7 @@
         </is>
       </c>
     </row>
-    <row r="412" spans="1:19" hidden="1">
+    <row r="412" spans="1:19">
       <c r="A412" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E007</t>
@@ -33649,7 +33638,7 @@
         </is>
       </c>
     </row>
-    <row r="413" spans="1:19" hidden="1">
+    <row r="413" spans="1:19">
       <c r="A413" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E008</t>
@@ -33795,7 +33784,7 @@
         </is>
       </c>
     </row>
-    <row r="415" spans="1:19" hidden="1">
+    <row r="415" spans="1:19">
       <c r="A415" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E010</t>
@@ -33865,7 +33854,7 @@
         </is>
       </c>
     </row>
-    <row r="416" spans="1:19" hidden="1">
+    <row r="416" spans="1:19">
       <c r="A416" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-NT-E011</t>
@@ -33943,7 +33932,7 @@
         </is>
       </c>
     </row>
-    <row r="417" spans="1:19" hidden="1">
+    <row r="417" spans="1:19">
       <c r="A417" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E001</t>
@@ -34013,7 +34002,7 @@
         </is>
       </c>
     </row>
-    <row r="418" spans="1:19" hidden="1">
+    <row r="418" spans="1:19">
       <c r="A418" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E002</t>
@@ -34083,7 +34072,7 @@
         </is>
       </c>
     </row>
-    <row r="419" spans="1:19" hidden="1">
+    <row r="419" spans="1:19">
       <c r="A419" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E003</t>
@@ -34153,7 +34142,7 @@
         </is>
       </c>
     </row>
-    <row r="420" spans="1:19" hidden="1">
+    <row r="420" spans="1:19">
       <c r="A420" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E004</t>
@@ -34223,7 +34212,7 @@
         </is>
       </c>
     </row>
-    <row r="421" spans="1:19" hidden="1">
+    <row r="421" spans="1:19">
       <c r="A421" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E005</t>
@@ -34293,7 +34282,7 @@
         </is>
       </c>
     </row>
-    <row r="422" spans="1:19" hidden="1">
+    <row r="422" spans="1:19">
       <c r="A422" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E006</t>
@@ -34363,7 +34352,7 @@
         </is>
       </c>
     </row>
-    <row r="423" spans="1:19" hidden="1">
+    <row r="423" spans="1:19">
       <c r="A423" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E007</t>
@@ -34433,7 +34422,7 @@
         </is>
       </c>
     </row>
-    <row r="424" spans="1:19" hidden="1">
+    <row r="424" spans="1:19">
       <c r="A424" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E008</t>
@@ -34503,7 +34492,7 @@
         </is>
       </c>
     </row>
-    <row r="425" spans="1:19" hidden="1">
+    <row r="425" spans="1:19">
       <c r="A425" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E009</t>
@@ -34573,7 +34562,7 @@
         </is>
       </c>
     </row>
-    <row r="426" spans="1:19" hidden="1">
+    <row r="426" spans="1:19">
       <c r="A426" t="inlineStr">
         <is>
           <t>OPVAL-P1A-S0-T-E010</t>
@@ -34643,7 +34632,7 @@
         </is>
       </c>
     </row>
-    <row r="427" spans="1:19" hidden="1">
+    <row r="427" spans="1:19">
       <c r="A427" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E001</t>
@@ -34718,7 +34707,7 @@
         </is>
       </c>
     </row>
-    <row r="428" spans="1:19" hidden="1">
+    <row r="428" spans="1:19">
       <c r="A428" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E002</t>
@@ -34788,7 +34777,7 @@
         </is>
       </c>
     </row>
-    <row r="429" spans="1:19" hidden="1">
+    <row r="429" spans="1:19">
       <c r="A429" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E003</t>
@@ -34858,7 +34847,7 @@
         </is>
       </c>
     </row>
-    <row r="430" spans="1:19" hidden="1">
+    <row r="430" spans="1:19">
       <c r="A430" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E004</t>
@@ -34928,7 +34917,7 @@
         </is>
       </c>
     </row>
-    <row r="431" spans="1:19" hidden="1">
+    <row r="431" spans="1:19">
       <c r="A431" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E005</t>
@@ -34998,7 +34987,7 @@
         </is>
       </c>
     </row>
-    <row r="432" spans="1:19" hidden="1">
+    <row r="432" spans="1:19">
       <c r="A432" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E006</t>
@@ -35068,7 +35057,7 @@
         </is>
       </c>
     </row>
-    <row r="433" spans="1:19" hidden="1">
+    <row r="433" spans="1:19">
       <c r="A433" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E007</t>
@@ -35138,7 +35127,7 @@
         </is>
       </c>
     </row>
-    <row r="434" spans="1:19" hidden="1">
+    <row r="434" spans="1:19">
       <c r="A434" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E008</t>
@@ -35213,7 +35202,7 @@
         </is>
       </c>
     </row>
-    <row r="435" spans="1:19" hidden="1">
+    <row r="435" spans="1:19">
       <c r="A435" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E009</t>
@@ -35283,7 +35272,7 @@
         </is>
       </c>
     </row>
-    <row r="436" spans="1:19" hidden="1">
+    <row r="436" spans="1:19">
       <c r="A436" t="inlineStr">
         <is>
           <t>OPVAL-P2A-S0-T-E010</t>
@@ -35353,7 +35342,7 @@
         </is>
       </c>
     </row>
-    <row r="437" spans="1:19" hidden="1">
+    <row r="437" spans="1:19">
       <c r="A437" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E001</t>
@@ -35423,7 +35412,7 @@
         </is>
       </c>
     </row>
-    <row r="438" spans="1:19" hidden="1">
+    <row r="438" spans="1:19">
       <c r="A438" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E002</t>
@@ -35493,7 +35482,7 @@
         </is>
       </c>
     </row>
-    <row r="439" spans="1:19" hidden="1">
+    <row r="439" spans="1:19">
       <c r="A439" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E003</t>
@@ -35563,7 +35552,7 @@
         </is>
       </c>
     </row>
-    <row r="440" spans="1:19" hidden="1">
+    <row r="440" spans="1:19">
       <c r="A440" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E004</t>
@@ -35709,7 +35698,7 @@
         </is>
       </c>
     </row>
-    <row r="442" spans="1:19" hidden="1">
+    <row r="442" spans="1:19">
       <c r="A442" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E006</t>
@@ -35779,7 +35768,7 @@
         </is>
       </c>
     </row>
-    <row r="443" spans="1:19" hidden="1">
+    <row r="443" spans="1:19">
       <c r="A443" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E007</t>
@@ -35849,7 +35838,7 @@
         </is>
       </c>
     </row>
-    <row r="444" spans="1:19" hidden="1">
+    <row r="444" spans="1:19">
       <c r="A444" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E008</t>
@@ -35919,7 +35908,7 @@
         </is>
       </c>
     </row>
-    <row r="445" spans="1:19" hidden="1">
+    <row r="445" spans="1:19">
       <c r="A445" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E009</t>
@@ -35989,7 +35978,7 @@
         </is>
       </c>
     </row>
-    <row r="446" spans="1:19" hidden="1">
+    <row r="446" spans="1:19">
       <c r="A446" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E010</t>
@@ -36059,7 +36048,7 @@
         </is>
       </c>
     </row>
-    <row r="447" spans="1:19" hidden="1">
+    <row r="447" spans="1:19">
       <c r="A447" t="inlineStr">
         <is>
           <t>OPVAL-P3A-S0-T-E011</t>
@@ -36132,7 +36121,7 @@
         </is>
       </c>
     </row>
-    <row r="448" spans="1:19" hidden="1">
+    <row r="448" spans="1:19">
       <c r="A448" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E001</t>
@@ -36202,7 +36191,7 @@
         </is>
       </c>
     </row>
-    <row r="449" spans="1:19" hidden="1">
+    <row r="449" spans="1:19">
       <c r="A449" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E002</t>
@@ -36272,7 +36261,7 @@
         </is>
       </c>
     </row>
-    <row r="450" spans="1:19" hidden="1">
+    <row r="450" spans="1:19">
       <c r="A450" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E003</t>
@@ -36342,7 +36331,7 @@
         </is>
       </c>
     </row>
-    <row r="451" spans="1:19" hidden="1">
+    <row r="451" spans="1:19">
       <c r="A451" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E004</t>
@@ -36488,7 +36477,7 @@
         </is>
       </c>
     </row>
-    <row r="453" spans="1:19" hidden="1">
+    <row r="453" spans="1:19">
       <c r="A453" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E006</t>
@@ -36558,7 +36547,7 @@
         </is>
       </c>
     </row>
-    <row r="454" spans="1:19" hidden="1">
+    <row r="454" spans="1:19">
       <c r="A454" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E007</t>
@@ -36628,7 +36617,7 @@
         </is>
       </c>
     </row>
-    <row r="455" spans="1:19" hidden="1">
+    <row r="455" spans="1:19">
       <c r="A455" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E008</t>
@@ -36698,7 +36687,7 @@
         </is>
       </c>
     </row>
-    <row r="456" spans="1:19" hidden="1">
+    <row r="456" spans="1:19">
       <c r="A456" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E009</t>
@@ -36768,7 +36757,7 @@
         </is>
       </c>
     </row>
-    <row r="457" spans="1:19" hidden="1">
+    <row r="457" spans="1:19">
       <c r="A457" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E010</t>
@@ -36838,7 +36827,7 @@
         </is>
       </c>
     </row>
-    <row r="458" spans="1:19" hidden="1">
+    <row r="458" spans="1:19">
       <c r="A458" t="inlineStr">
         <is>
           <t>OPVAL-P4A-S0-T-E011</t>
@@ -36916,7 +36905,7 @@
         </is>
       </c>
     </row>
-    <row r="459" spans="1:19" hidden="1">
+    <row r="459" spans="1:19">
       <c r="A459" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E001</t>
@@ -36986,7 +36975,7 @@
         </is>
       </c>
     </row>
-    <row r="460" spans="1:19" hidden="1">
+    <row r="460" spans="1:19">
       <c r="A460" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E002</t>
@@ -37056,7 +37045,7 @@
         </is>
       </c>
     </row>
-    <row r="461" spans="1:19" hidden="1">
+    <row r="461" spans="1:19">
       <c r="A461" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E003</t>
@@ -37126,7 +37115,7 @@
         </is>
       </c>
     </row>
-    <row r="462" spans="1:19" hidden="1">
+    <row r="462" spans="1:19">
       <c r="A462" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E004</t>
@@ -37196,7 +37185,7 @@
         </is>
       </c>
     </row>
-    <row r="463" spans="1:19" hidden="1">
+    <row r="463" spans="1:19">
       <c r="A463" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E005</t>
@@ -37266,7 +37255,7 @@
         </is>
       </c>
     </row>
-    <row r="464" spans="1:19" hidden="1">
+    <row r="464" spans="1:19">
       <c r="A464" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E006</t>
@@ -37336,7 +37325,7 @@
         </is>
       </c>
     </row>
-    <row r="465" spans="1:19" hidden="1">
+    <row r="465" spans="1:19">
       <c r="A465" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E007</t>
@@ -37406,7 +37395,7 @@
         </is>
       </c>
     </row>
-    <row r="466" spans="1:19" hidden="1">
+    <row r="466" spans="1:19">
       <c r="A466" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E008</t>
@@ -37476,7 +37465,7 @@
         </is>
       </c>
     </row>
-    <row r="467" spans="1:19" hidden="1">
+    <row r="467" spans="1:19">
       <c r="A467" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E009</t>
@@ -37546,7 +37535,7 @@
         </is>
       </c>
     </row>
-    <row r="468" spans="1:19" hidden="1">
+    <row r="468" spans="1:19">
       <c r="A468" t="inlineStr">
         <is>
           <t>OPVAL-P5A-S0-T-E010</t>
@@ -37616,7 +37605,7 @@
         </is>
       </c>
     </row>
-    <row r="469" spans="1:19" hidden="1">
+    <row r="469" spans="1:19">
       <c r="A469" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E001</t>
@@ -37686,7 +37675,7 @@
         </is>
       </c>
     </row>
-    <row r="470" spans="1:19" hidden="1">
+    <row r="470" spans="1:19">
       <c r="A470" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E002</t>
@@ -37756,7 +37745,7 @@
         </is>
       </c>
     </row>
-    <row r="471" spans="1:19" hidden="1">
+    <row r="471" spans="1:19">
       <c r="A471" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E003</t>
@@ -37826,7 +37815,7 @@
         </is>
       </c>
     </row>
-    <row r="472" spans="1:19" hidden="1">
+    <row r="472" spans="1:19">
       <c r="A472" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E004</t>
@@ -37896,7 +37885,7 @@
         </is>
       </c>
     </row>
-    <row r="473" spans="1:19" hidden="1">
+    <row r="473" spans="1:19">
       <c r="A473" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E005</t>
@@ -37966,7 +37955,7 @@
         </is>
       </c>
     </row>
-    <row r="474" spans="1:19" hidden="1">
+    <row r="474" spans="1:19">
       <c r="A474" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E006</t>
@@ -38036,7 +38025,7 @@
         </is>
       </c>
     </row>
-    <row r="475" spans="1:19" hidden="1">
+    <row r="475" spans="1:19">
       <c r="A475" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E007</t>
@@ -38106,7 +38095,7 @@
         </is>
       </c>
     </row>
-    <row r="476" spans="1:19" hidden="1">
+    <row r="476" spans="1:19">
       <c r="A476" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E008</t>
@@ -38176,7 +38165,7 @@
         </is>
       </c>
     </row>
-    <row r="477" spans="1:19" hidden="1">
+    <row r="477" spans="1:19">
       <c r="A477" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E009</t>
@@ -38246,7 +38235,7 @@
         </is>
       </c>
     </row>
-    <row r="478" spans="1:19" hidden="1">
+    <row r="478" spans="1:19">
       <c r="A478" t="inlineStr">
         <is>
           <t>OPVAL-P6A-S0-T-E010</t>
@@ -38316,7 +38305,7 @@
         </is>
       </c>
     </row>
-    <row r="479" spans="1:19" hidden="1">
+    <row r="479" spans="1:19">
       <c r="A479" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E001</t>
@@ -38386,7 +38375,7 @@
         </is>
       </c>
     </row>
-    <row r="480" spans="1:19" hidden="1">
+    <row r="480" spans="1:19">
       <c r="A480" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E002</t>
@@ -38456,7 +38445,7 @@
         </is>
       </c>
     </row>
-    <row r="481" spans="1:19" hidden="1">
+    <row r="481" spans="1:19">
       <c r="A481" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E003</t>
@@ -38526,7 +38515,7 @@
         </is>
       </c>
     </row>
-    <row r="482" spans="1:19" hidden="1">
+    <row r="482" spans="1:19">
       <c r="A482" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E004</t>
@@ -38596,7 +38585,7 @@
         </is>
       </c>
     </row>
-    <row r="483" spans="1:19" hidden="1">
+    <row r="483" spans="1:19">
       <c r="A483" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E005</t>
@@ -38666,7 +38655,7 @@
         </is>
       </c>
     </row>
-    <row r="484" spans="1:19" hidden="1">
+    <row r="484" spans="1:19">
       <c r="A484" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E006</t>
@@ -38736,7 +38725,7 @@
         </is>
       </c>
     </row>
-    <row r="485" spans="1:19" hidden="1">
+    <row r="485" spans="1:19">
       <c r="A485" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E007</t>
@@ -38806,7 +38795,7 @@
         </is>
       </c>
     </row>
-    <row r="486" spans="1:19" hidden="1">
+    <row r="486" spans="1:19">
       <c r="A486" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E008</t>
@@ -38876,7 +38865,7 @@
         </is>
       </c>
     </row>
-    <row r="487" spans="1:19" hidden="1">
+    <row r="487" spans="1:19">
       <c r="A487" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E009</t>
@@ -38946,7 +38935,7 @@
         </is>
       </c>
     </row>
-    <row r="488" spans="1:19" hidden="1">
+    <row r="488" spans="1:19">
       <c r="A488" t="inlineStr">
         <is>
           <t>OPVAL-P7A-S0-T-E010</t>
@@ -39016,7 +39005,7 @@
         </is>
       </c>
     </row>
-    <row r="489" spans="1:19" hidden="1">
+    <row r="489" spans="1:19">
       <c r="A489" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E001</t>
@@ -39086,7 +39075,7 @@
         </is>
       </c>
     </row>
-    <row r="490" spans="1:19" hidden="1">
+    <row r="490" spans="1:19">
       <c r="A490" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E002</t>
@@ -39156,7 +39145,7 @@
         </is>
       </c>
     </row>
-    <row r="491" spans="1:19" hidden="1">
+    <row r="491" spans="1:19">
       <c r="A491" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E003</t>
@@ -39226,7 +39215,7 @@
         </is>
       </c>
     </row>
-    <row r="492" spans="1:19" hidden="1">
+    <row r="492" spans="1:19">
       <c r="A492" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E004</t>
@@ -39296,7 +39285,7 @@
         </is>
       </c>
     </row>
-    <row r="493" spans="1:19" hidden="1">
+    <row r="493" spans="1:19">
       <c r="A493" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E005</t>
@@ -39366,7 +39355,7 @@
         </is>
       </c>
     </row>
-    <row r="494" spans="1:19" hidden="1">
+    <row r="494" spans="1:19">
       <c r="A494" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E006</t>
@@ -39436,7 +39425,7 @@
         </is>
       </c>
     </row>
-    <row r="495" spans="1:19" hidden="1">
+    <row r="495" spans="1:19">
       <c r="A495" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E007</t>
@@ -39506,7 +39495,7 @@
         </is>
       </c>
     </row>
-    <row r="496" spans="1:19" hidden="1">
+    <row r="496" spans="1:19">
       <c r="A496" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E008</t>
@@ -39576,7 +39565,7 @@
         </is>
       </c>
     </row>
-    <row r="497" spans="1:19" hidden="1">
+    <row r="497" spans="1:19">
       <c r="A497" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E009</t>
@@ -39646,7 +39635,7 @@
         </is>
       </c>
     </row>
-    <row r="498" spans="1:19" hidden="1">
+    <row r="498" spans="1:19">
       <c r="A498" t="inlineStr">
         <is>
           <t>OPVAL-P8A-S0-T-E010</t>
@@ -39716,7 +39705,7 @@
         </is>
       </c>
     </row>
-    <row r="499" spans="1:19" hidden="1">
+    <row r="499" spans="1:19">
       <c r="A499" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E001</t>
@@ -39786,7 +39775,7 @@
         </is>
       </c>
     </row>
-    <row r="500" spans="1:19" hidden="1">
+    <row r="500" spans="1:19">
       <c r="A500" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E002</t>
@@ -39856,7 +39845,7 @@
         </is>
       </c>
     </row>
-    <row r="501" spans="1:19" hidden="1">
+    <row r="501" spans="1:19">
       <c r="A501" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E003</t>
@@ -39926,7 +39915,7 @@
         </is>
       </c>
     </row>
-    <row r="502" spans="1:19" hidden="1">
+    <row r="502" spans="1:19">
       <c r="A502" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E004</t>
@@ -39996,7 +39985,7 @@
         </is>
       </c>
     </row>
-    <row r="503" spans="1:19" hidden="1">
+    <row r="503" spans="1:19">
       <c r="A503" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E005</t>
@@ -40066,7 +40055,7 @@
         </is>
       </c>
     </row>
-    <row r="504" spans="1:19" hidden="1">
+    <row r="504" spans="1:19">
       <c r="A504" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E006</t>
@@ -40136,7 +40125,7 @@
         </is>
       </c>
     </row>
-    <row r="505" spans="1:19" hidden="1">
+    <row r="505" spans="1:19">
       <c r="A505" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E007</t>
@@ -40206,7 +40195,7 @@
         </is>
       </c>
     </row>
-    <row r="506" spans="1:19" hidden="1">
+    <row r="506" spans="1:19">
       <c r="A506" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E008</t>
@@ -40276,7 +40265,7 @@
         </is>
       </c>
     </row>
-    <row r="507" spans="1:19" hidden="1">
+    <row r="507" spans="1:19">
       <c r="A507" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E009</t>
@@ -40346,7 +40335,7 @@
         </is>
       </c>
     </row>
-    <row r="508" spans="1:19" hidden="1">
+    <row r="508" spans="1:19">
       <c r="A508" t="inlineStr">
         <is>
           <t>OPVAL-P9A-S0-T-E010</t>
@@ -40416,7 +40405,7 @@
         </is>
       </c>
     </row>
-    <row r="509" spans="1:19" hidden="1">
+    <row r="509" spans="1:19">
       <c r="A509" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E001</t>
@@ -40491,7 +40480,7 @@
         </is>
       </c>
     </row>
-    <row r="510" spans="1:19" hidden="1">
+    <row r="510" spans="1:19">
       <c r="A510" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E002</t>
@@ -40566,7 +40555,7 @@
         </is>
       </c>
     </row>
-    <row r="511" spans="1:19" hidden="1">
+    <row r="511" spans="1:19">
       <c r="A511" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E003</t>
@@ -40641,7 +40630,7 @@
         </is>
       </c>
     </row>
-    <row r="512" spans="1:19" hidden="1">
+    <row r="512" spans="1:19">
       <c r="A512" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E004</t>
@@ -40716,7 +40705,7 @@
         </is>
       </c>
     </row>
-    <row r="513" spans="1:19" hidden="1">
+    <row r="513" spans="1:19">
       <c r="A513" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E005</t>
@@ -40791,7 +40780,7 @@
         </is>
       </c>
     </row>
-    <row r="514" spans="1:19" hidden="1">
+    <row r="514" spans="1:19">
       <c r="A514" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E006</t>
@@ -40866,7 +40855,7 @@
         </is>
       </c>
     </row>
-    <row r="515" spans="1:19" hidden="1">
+    <row r="515" spans="1:19">
       <c r="A515" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E007</t>
@@ -40941,7 +40930,7 @@
         </is>
       </c>
     </row>
-    <row r="516" spans="1:19" hidden="1">
+    <row r="516" spans="1:19">
       <c r="A516" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E008</t>
@@ -41016,7 +41005,7 @@
         </is>
       </c>
     </row>
-    <row r="517" spans="1:19" hidden="1">
+    <row r="517" spans="1:19">
       <c r="A517" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E009</t>
@@ -41091,7 +41080,7 @@
         </is>
       </c>
     </row>
-    <row r="518" spans="1:19" hidden="1">
+    <row r="518" spans="1:19">
       <c r="A518" t="inlineStr">
         <is>
           <t>PROSP-P1P-S0-T-E010</t>

--- a/verification/registry-records.xlsx
+++ b/verification/registry-records.xlsx
@@ -2879,20 +2879,20 @@
       <x:c r="B5" s="25" t="str">
         <x:v>No Table</x:v>
       </x:c>
-      <x:c r="C5" s="22" t="n">
+      <x:c r="C5" s="22">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A5,'S0 Registry Executions'!$G$2:$G$518,B5,'S0 Registry Executions'!$M$2:$M$518,"Yes")</x:f>
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D5" s="22" t="n">
+      <x:c r="D5" s="22">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A5,'S0 Registry Executions'!$G$2:$G$518,B5,'S0 Registry Executions'!$M$2:$M$518,"No")</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E5" s="22" t="n">
-        <x:f t="shared" ref="E5:E10" si="0">C5+D5</x:f>
+      <x:c r="E5" s="22">
+        <x:f>C5+D5</x:f>
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F5" s="27" t="n">
-        <x:f t="shared" ref="F5:F10" si="1">IFERROR(D5/E5,0)</x:f>
+      <x:c r="F5" s="27">
+        <x:f>IFERROR(D5/E5,0)</x:f>
         <x:v>0.26229508196721313</x:v>
       </x:c>
       <x:c r="G5" s="24" t="str">
@@ -2912,20 +2912,20 @@
       <x:c r="B6" s="25" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="C6" s="22" t="n">
+      <x:c r="C6" s="22">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A6,'S0 Registry Executions'!$G$2:$G$518,B6,'S0 Registry Executions'!$M$2:$M$518,"Yes")</x:f>
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D6" s="22" t="n">
+      <x:c r="D6" s="22">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A6,'S0 Registry Executions'!$G$2:$G$518,B6,'S0 Registry Executions'!$M$2:$M$518,"No")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E6" s="22" t="n">
-        <x:f t="shared" si="0">C6+D6</x:f>
+      <x:c r="E6" s="22">
+        <x:f>C6+D6</x:f>
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="n">
-        <x:f t="shared" si="1">IFERROR(D6/E6,0)</x:f>
+      <x:c r="F6" s="27">
+        <x:f>IFERROR(D6/E6,0)</x:f>
         <x:v>0.021739130434782608</x:v>
       </x:c>
       <x:c r="G6" s="24" t="str">
@@ -2945,20 +2945,20 @@
       <x:c r="B7" t="str">
         <x:v>No Table</x:v>
       </x:c>
-      <x:c r="C7" t="n">
+      <x:c r="C7">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A7,'S0 Registry Executions'!$G$2:$G$518,B7,'S0 Registry Executions'!$M$2:$M$518,"Yes")</x:f>
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D7" t="n">
+      <x:c r="D7">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A7,'S0 Registry Executions'!$G$2:$G$518,B7,'S0 Registry Executions'!$M$2:$M$518,"No")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E7" t="n">
-        <x:f t="shared" si="0">C7+D7</x:f>
+      <x:c r="E7">
+        <x:f>C7+D7</x:f>
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F7" s="28" t="n">
-        <x:f t="shared" si="1">IFERROR(D7/E7,0)</x:f>
+      <x:c r="F7" s="28">
+        <x:f>IFERROR(D7/E7,0)</x:f>
         <x:v>0.09090909090909091</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
@@ -2978,20 +2978,20 @@
       <x:c r="B8" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="C8" t="n">
+      <x:c r="C8">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A8,'S0 Registry Executions'!$G$2:$G$518,B8,'S0 Registry Executions'!$M$2:$M$518,"Yes")</x:f>
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D8" t="n">
+      <x:c r="D8">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A8,'S0 Registry Executions'!$G$2:$G$518,B8,'S0 Registry Executions'!$M$2:$M$518,"No")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E8" t="n">
-        <x:f t="shared" si="0">C8+D8</x:f>
+      <x:c r="E8">
+        <x:f>C8+D8</x:f>
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F8" s="28" t="n">
-        <x:f t="shared" si="1">IFERROR(D8/E8,0)</x:f>
+      <x:c r="F8" s="28">
+        <x:f>IFERROR(D8/E8,0)</x:f>
         <x:v>0.03225806451612903</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
@@ -3011,20 +3011,20 @@
       <x:c r="B9" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="C9" t="n">
+      <x:c r="C9">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A9,'S0 Registry Executions'!$G$2:$G$518,B9,'S0 Registry Executions'!$M$2:$M$518,"Yes")</x:f>
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D9" t="n">
+      <x:c r="D9">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A9,'S0 Registry Executions'!$G$2:$G$518,B9,'S0 Registry Executions'!$M$2:$M$518,"No")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" t="n">
-        <x:f t="shared" si="0">C9+D9</x:f>
+      <x:c r="E9">
+        <x:f>C9+D9</x:f>
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F9" s="28" t="n">
-        <x:f t="shared" si="1">IFERROR(D9/E9,0)</x:f>
+      <x:c r="F9" s="28">
+        <x:f>IFERROR(D9/E9,0)</x:f>
         <x:v>0.10891089108910891</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
@@ -3044,20 +3044,20 @@
       <x:c r="B10" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="C10" t="n">
+      <x:c r="C10">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A10,'S0 Registry Executions'!$G$2:$G$518,B10,'S0 Registry Executions'!$M$2:$M$518,"Yes")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D10" t="n">
+      <x:c r="D10">
         <x:f>COUNTIFS('S0 Registry Executions'!$C$2:$C$518,A10,'S0 Registry Executions'!$G$2:$G$518,B10,'S0 Registry Executions'!$M$2:$M$518,"No")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" t="n">
-        <x:f t="shared" si="0">C10+D10</x:f>
+      <x:c r="E10">
+        <x:f>C10+D10</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F10" s="28" t="n">
-        <x:f t="shared" si="1">IFERROR(D10/E10,0)</x:f>
+      <x:c r="F10" s="28">
+        <x:f>IFERROR(D10/E10,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
@@ -3095,19 +3095,19 @@
       <x:c r="A13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B13" t="n">
+      <x:c r="B13">
         <x:f>SUMIFS($D$5:$D$10,$B$5:$B$10,A13,$G$5:$G$10,"Yes")</x:f>
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C13" t="n">
+      <x:c r="C13">
         <x:f>SUMIFS($E$5:$E$10,$B$5:$B$10,A13,$G$5:$G$10,"Yes")</x:f>
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="n">
+      <x:c r="D13" s="28">
         <x:f>IFERROR(B13/C13,0)</x:f>
         <x:v>0.18552036199095023</x:v>
       </x:c>
-      <x:c r="E13" t="n">
+      <x:c r="E13">
         <x:f>C13-B13</x:f>
         <x:v>180</x:v>
       </x:c>
@@ -3125,19 +3125,19 @@
       <x:c r="A14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B14" t="n">
+      <x:c r="B14">
         <x:f>SUMIFS($D$5:$D$10,$B$5:$B$10,A14,$G$5:$G$10,"Yes")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C14" t="n">
+      <x:c r="C14">
         <x:f>SUMIFS($E$5:$E$10,$B$5:$B$10,A14,$G$5:$G$10,"Yes")</x:f>
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="n">
+      <x:c r="D14" s="28">
         <x:f>IFERROR(B14/C14,0)</x:f>
         <x:v>0.02702702702702703</x:v>
       </x:c>
-      <x:c r="E14" t="n">
+      <x:c r="E14">
         <x:f>C14-B14</x:f>
         <x:v>180</x:v>
       </x:c>
@@ -3172,23 +3172,23 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="n">
+      <x:c r="A18">
         <x:f>COUNTA('S0 Registry Executions'!A2:A518)</x:f>
         <x:v>517</x:v>
       </x:c>
-      <x:c r="B18" t="n">
+      <x:c r="B18">
         <x:f>COUNTIF('S0 Registry Executions'!M2:M518,"Yes")</x:f>
         <x:v>460</x:v>
       </x:c>
-      <x:c r="C18" t="n">
+      <x:c r="C18">
         <x:f>COUNTIF('S0 Registry Executions'!M2:M518,"No")</x:f>
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D18" t="n">
+      <x:c r="D18">
         <x:f>COUNTIF('S0 Registry Executions'!S2:S518,"Lineage only")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F18" t="n">
+      <x:c r="F18">
         <x:f>SUM(C13:C14)</x:f>
         <x:v>406</x:v>
       </x:c>
